--- a/服务化需求.xlsx
+++ b/服务化需求.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>模块</t>
   </si>
@@ -66,7 +66,23 @@
   </si>
   <si>
     <t>1.算子层面跑不同shape后端实现
-2.量化策略配置，目前使用内置的量化策略，要做成可配置</t>
+2.接入Component Roofline算子性能评估引擎</t>
+  </si>
+  <si>
+    <t>算子管理</t>
+  </si>
+  <si>
+    <t>支持用户配置自定义算子：
+1.自定义算子编辑页面开发
+2.自定义算子crud接口开发</t>
+  </si>
+  <si>
+    <t>硬件管理</t>
+  </si>
+  <si>
+    <t>支持用户配置自定义硬件：
+1.支持用户配置自定义集群
+2.支持用户配置自定义芯片</t>
   </si>
 </sst>
 </file>
@@ -1000,8 +1016,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="37.375" customWidth="1"/>
@@ -1061,6 +1077,28 @@
       </c>
       <c r="C5">
         <v>7.3</v>
+      </c>
+    </row>
+    <row r="6" ht="40.5" spans="1:3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="7" ht="40.5" spans="1:3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>6.27</v>
       </c>
     </row>
   </sheetData>
